--- a/Result/profitability/2349.xlsx
+++ b/Result/profitability/2349.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.09</v>
+        <v>-0.08624999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>14.825</v>
+        <v>14.625</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.48</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.14875</v>
+        <v>-0.1525</v>
       </c>
       <c r="N3" t="n">
-        <v>12.78</v>
+        <v>11.95</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2125</v>
+        <v>-0.21125</v>
       </c>
       <c r="N4" t="n">
-        <v>10.04375</v>
+        <v>10.13875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-1.31</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3775</v>
+        <v>-0.34625</v>
       </c>
       <c r="N5" t="n">
-        <v>5.2225</v>
+        <v>5.17375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.32</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.38875</v>
+        <v>-0.37125</v>
       </c>
       <c r="N6" t="n">
-        <v>3.94875</v>
+        <v>4.48875</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>-0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.43625</v>
+        <v>-0.43125</v>
       </c>
       <c r="N7" t="n">
-        <v>2.73625</v>
+        <v>2.35375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1394,7 +1394,7 @@
         <v>-0.47625</v>
       </c>
       <c r="N8" t="n">
-        <v>1.785</v>
+        <v>0.9062500000000002</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2349</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2172</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1864</v>
+      </c>
+      <c r="E75" t="n">
+        <v>308</v>
+      </c>
+      <c r="F75" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-1.45%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>178</v>
+      </c>
+      <c r="J75" t="n">
+        <v>146</v>
+      </c>
+      <c r="K75" t="n">
+        <v>16</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.885</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-7.030000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3314474304573315</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.08695652173913</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.3900000000000006</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.026767330130405</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
